--- a/SQL REVISION TRACKER/SQL_Revision_Tracker_Main.xlsx
+++ b/SQL REVISION TRACKER/SQL_Revision_Tracker_Main.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Analytics\Structure Query Language (SQL)\SQL REVISION TRACKER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C46B017D-B384-43F4-9076-B6391A573F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65A57416-FA77-4C4B-A782-7F59A7AC341A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="25">
   <si>
     <t>SQL Study &amp; Revision Tracker</t>
   </si>
@@ -93,6 +93,12 @@
   </si>
   <si>
     <t>Done</t>
+  </si>
+  <si>
+    <t>Data Constraints and Aggregate Function</t>
+  </si>
+  <si>
+    <t>Completed</t>
   </si>
 </sst>
 </file>
@@ -124,7 +130,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -149,6 +155,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -180,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -200,12 +218,18 @@
     <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -509,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -520,28 +544,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="F5" s="4" t="s">
@@ -599,17 +623,17 @@
       <c r="E7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>17</v>
+      <c r="H7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -629,12 +653,12 @@
         <v>46172</v>
       </c>
       <c r="G10" s="6">
-        <f>F10+5</f>
-        <v>46177</v>
+        <f>A12+5</f>
+        <v>46174</v>
       </c>
       <c r="H10" s="6">
-        <f>G10+15</f>
-        <v>46192</v>
+        <f>A12+15</f>
+        <v>46184</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -683,11 +707,11 @@
       <c r="E12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>17</v>
+      <c r="G12" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>17</v>
@@ -708,18 +732,9 @@
       <c r="I13" s="3"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="F14" s="6">
-        <f>A16+3</f>
-        <v>3</v>
-      </c>
-      <c r="G14" s="6">
-        <f>F14+5</f>
-        <v>8</v>
-      </c>
-      <c r="H14" s="6">
-        <f>G14+15</f>
-        <v>23</v>
-      </c>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
@@ -785,91 +800,154 @@
       <c r="I17" s="3"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
+      <c r="A19" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="5"/>
+      <c r="B20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
+      <c r="I20" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
+      <c r="A21" s="5"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
+      <c r="I21" s="2"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="5"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="2"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="5"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="2"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A24:I26"/>
+    <mergeCell ref="A27:I29"/>
     <mergeCell ref="A1:I2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7:H8 F12:H12 F16:H16" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7:H8 F12:H12 F16:H16 F20:H23" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Done, Pending"</formula1>
     </dataValidation>
   </dataValidations>
